--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Functional score profile for mRS, NIHSS, ASPECTS, GCS-like score categories, Hunt-Hess, ABCD2, CHA2DS2-VASc and THRIVE.</t>
+    <t>Observation profile for functional or severity scores such as mRS, NIHSS, ASPECTS, Hunt-Hess, ABCD2, CHA2DS2-VASc and THRIVE.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -741,7 +741,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -815,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Functional or severity score instrument</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -859,10 +859,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -913,10 +913,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1032,7 +1032,7 @@
 CodeableConceptinteger</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Recorded score value</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1076,6 +1076,9 @@
   </si>
   <si>
     <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Actual result</t>
   </si>
   <si>
     <t>http://tecnomod-um.org/ValueSet/mrs-score-vs</t>
@@ -1830,98 +1833,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2115,10 +2120,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2200,7 +2205,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>
@@ -5862,7 +5867,7 @@
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>324</v>
@@ -5900,7 +5905,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5953,10 +5958,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5982,16 +5987,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6019,10 +6024,10 @@
         <v>258</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6040,7 +6045,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6049,7 +6054,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6067,7 +6072,7 @@
         <v>139</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6075,14 +6080,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6104,16 +6109,16 @@
         <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6141,10 +6146,10 @@
         <v>258</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6162,7 +6167,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6183,24 +6188,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6223,19 +6228,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6284,7 +6289,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6308,10 +6313,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6319,10 +6324,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6348,13 +6353,13 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6380,13 +6385,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6404,7 +6409,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6413,7 +6418,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6425,24 +6430,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6465,16 +6470,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6524,7 +6529,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6533,7 +6538,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6551,7 +6556,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6559,10 +6564,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6588,16 +6593,16 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6622,13 +6627,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6646,7 +6651,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6670,10 +6675,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6681,10 +6686,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6707,16 +6712,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6766,7 +6771,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6778,7 +6783,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6787,24 +6792,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6827,16 +6832,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6886,7 +6891,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6907,24 +6912,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6950,16 +6955,16 @@
         <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7008,7 +7013,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7020,7 +7025,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7032,10 +7037,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7043,10 +7048,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7161,10 +7166,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7281,10 +7286,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7403,10 +7408,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7429,13 +7434,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7486,7 +7491,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7495,7 +7500,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7510,10 +7515,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7521,10 +7526,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7547,13 +7552,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7604,7 +7609,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7613,7 +7618,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7628,10 +7633,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7639,10 +7644,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7668,10 +7673,10 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7701,10 +7706,10 @@
         <v>258</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7722,7 +7727,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7746,10 +7751,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7757,10 +7762,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7786,16 +7791,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7823,10 +7828,10 @@
         <v>248</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7844,7 +7849,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7865,13 +7870,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7879,10 +7884,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7908,16 +7913,16 @@
         <v>243</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7942,13 +7947,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7966,7 +7971,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7987,13 +7992,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8001,10 +8006,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8027,17 +8032,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8086,7 +8091,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8113,7 +8118,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8121,10 +8126,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8147,13 +8152,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8204,7 +8209,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8213,7 +8218,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8228,10 +8233,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8239,10 +8244,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8265,16 +8270,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8324,7 +8329,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8348,7 +8353,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>209</v>
@@ -8359,10 +8364,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8385,16 +8390,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8444,7 +8449,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8468,10 +8473,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8479,10 +8484,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8508,16 +8513,16 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8566,7 +8571,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8590,10 +8595,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8606,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8719,10 +8724,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8839,10 +8844,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8961,10 +8966,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8990,13 +8995,13 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>257</v>
@@ -9024,13 +9029,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9048,7 +9053,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9069,7 +9074,7 @@
         <v>262</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>264</v>
@@ -9083,10 +9088,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9109,16 +9114,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>326</v>
@@ -9170,7 +9175,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9191,7 +9196,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>330</v>
@@ -9205,10 +9210,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9234,16 +9239,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9271,10 +9276,10 @@
         <v>258</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9292,7 +9297,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9319,7 +9324,7 @@
         <v>139</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9327,14 +9332,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9356,16 +9361,16 @@
         <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9393,10 +9398,10 @@
         <v>258</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9414,7 +9419,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9435,24 +9440,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9478,16 +9483,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9536,7 +9541,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9560,10 +9565,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1052,10 +1052,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1070,18 +1066,6 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/mrs-score-vs</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1944,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.0234375" customWidth="true" bestFit="true"/>
@@ -5714,7 +5698,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>321</v>
       </c>
@@ -5791,14 +5775,16 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>321</v>
@@ -5810,7 +5796,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5822,28 +5808,26 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5861,22 +5845,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5903,9 +5887,11 @@
       <c r="X33" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="Y33" s="2"/>
+      <c r="Y33" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5923,7 +5909,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5932,7 +5918,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5944,35 +5930,35 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5987,16 +5973,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6024,10 +6010,10 @@
         <v>258</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6045,16 +6031,16 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6066,28 +6052,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6106,19 +6092,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6143,31 +6129,31 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6188,24 +6174,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6216,7 +6202,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6228,20 +6214,18 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6265,13 +6249,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6289,16 +6273,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6310,24 +6294,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6350,16 +6334,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6385,13 +6369,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6409,7 +6393,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6418,7 +6402,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6430,16 +6414,16 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6470,18 +6454,20 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6505,13 +6491,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6538,7 +6524,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6553,10 +6539,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6564,10 +6550,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6590,20 +6576,18 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6627,13 +6611,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6651,7 +6635,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6663,7 +6647,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6672,24 +6656,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6712,16 +6696,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6771,7 +6755,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6783,7 +6767,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>397</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6792,24 +6776,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6820,7 +6804,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6832,18 +6816,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>403</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6891,19 +6877,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>411</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6912,24 +6898,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6940,7 +6926,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6952,20 +6938,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>191</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7013,19 +6995,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>193</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7037,10 +7019,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>418</v>
+        <v>195</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7048,21 +7030,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7074,15 +7056,17 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7131,19 +7115,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7166,14 +7150,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7186,24 +7170,26 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7251,7 +7237,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7278,7 +7264,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7286,46 +7272,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>419</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7373,19 +7355,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>204</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7397,10 +7379,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>139</v>
+        <v>422</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7408,10 +7390,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7434,7 +7416,7 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>424</v>
@@ -7491,7 +7473,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7500,7 +7482,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7515,10 +7497,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7526,10 +7508,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7552,13 +7534,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7585,13 +7567,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7609,7 +7591,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7618,7 +7600,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7633,10 +7615,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7644,10 +7626,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7673,13 +7655,17 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7703,13 +7689,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7727,7 +7713,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7748,13 +7734,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7762,10 +7748,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7776,7 +7762,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7791,16 +7777,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7825,13 +7811,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
+        <v>365</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7849,13 +7835,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7870,13 +7856,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7884,10 +7870,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7898,7 +7884,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7910,19 +7896,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>450</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7947,13 +7931,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7971,13 +7955,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7992,13 +7976,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>356</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8006,10 +7990,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8032,18 +8016,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8091,7 +8073,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8100,7 +8082,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8115,7 +8097,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>459</v>
@@ -8140,7 +8122,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8149,7 +8131,7 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>461</v>
@@ -8160,7 +8142,9 @@
       <c r="M52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8215,10 +8199,10 @@
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8233,10 +8217,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>209</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8244,10 +8228,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8270,16 +8254,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8329,7 +8313,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8353,10 +8337,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>209</v>
+        <v>471</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8364,10 +8348,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8390,7 +8374,7 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>473</v>
@@ -8401,7 +8385,9 @@
       <c r="N54" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8449,7 +8435,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8458,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8473,10 +8459,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8484,10 +8470,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8498,7 +8484,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8507,23 +8493,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>191</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8571,19 +8553,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8595,10 +8577,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>483</v>
+        <v>195</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8606,21 +8588,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8632,15 +8614,17 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8689,19 +8673,19 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8724,14 +8708,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8744,24 +8728,26 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8809,7 +8795,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8836,7 +8822,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8844,45 +8830,45 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>202</v>
+        <v>483</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>203</v>
+        <v>484</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
+        <v>485</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8907,13 +8893,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8931,34 +8917,34 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>204</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8966,10 +8952,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8977,7 +8963,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>94</v>
@@ -8992,19 +8978,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>243</v>
+        <v>490</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
+        <v>324</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9029,13 +9015,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9053,16 +9039,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9071,19 +9057,19 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>493</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9111,22 +9097,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>497</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9151,13 +9137,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9196,35 +9182,35 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9239,16 +9225,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>343</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>344</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>502</v>
+        <v>345</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9276,10 +9262,10 @@
         <v>258</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9297,13 +9283,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9318,28 +9304,28 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9358,19 +9344,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>348</v>
+        <v>500</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>349</v>
+        <v>501</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9395,13 +9381,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9419,7 +9405,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9440,142 +9426,20 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP63">
+  <autoFilter ref="A1:AP62">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9585,7 +9449,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/functional-score-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/functional-score-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -485,7 +485,7 @@
     <t>observationTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/observation-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/observation-timing-context-ext}
 </t>
   </si>
   <si>
@@ -830,7 +830,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/functional-score-vs</t>
+    <t>http://qualityregistry.org/ValueSet/functional-score-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -855,7 +855,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
